--- a/output/Data and Chart Outputs/south_korea_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/south_korea_demand_daily.xlsx
@@ -156,7 +156,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>South Korea monthly peak and minimum demand and supply capability (KPX EPSIS) (to Sep/26)</a:t>
+              <a:t>South Korea monthly peak and minimum demand and supply capability (KPX EPSIS) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -192,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$106</f>
+              <f>'Chart'!$A$2:$A$107</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$106</f>
+              <f>'Chart'!$B$2:$B$107</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -228,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$106</f>
+              <f>'Chart'!$A$2:$A$107</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$106</f>
+              <f>'Chart'!$C$2:$C$107</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -264,12 +264,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$106</f>
+              <f>'Chart'!$A$2:$A$107</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$106</f>
+              <f>'Chart'!$D$2:$D$107</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1954,6 +1954,20 @@
       </c>
       <c r="D106" t="n">
         <v>98.39366666666668</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B107" t="n">
+        <v>75.404</v>
+      </c>
+      <c r="C107" t="n">
+        <v>42.326</v>
+      </c>
+      <c r="D107" t="n">
+        <v>91.73203703703703</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +1982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4301"/>
+  <dimension ref="A1:G4319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88968,6 +88982,420 @@
         <v>35.7</v>
       </c>
     </row>
+    <row r="4302">
+      <c r="A4302" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B4302" t="n">
+        <v>161493</v>
+      </c>
+      <c r="C4302" t="n">
+        <v>88563</v>
+      </c>
+      <c r="D4302" t="n">
+        <v>62612</v>
+      </c>
+      <c r="E4302" t="n">
+        <v>43721</v>
+      </c>
+      <c r="F4302" t="n">
+        <v>25951</v>
+      </c>
+      <c r="G4302" t="n">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B4303" t="n">
+        <v>161493</v>
+      </c>
+      <c r="C4303" t="n">
+        <v>87838</v>
+      </c>
+      <c r="D4303" t="n">
+        <v>62992</v>
+      </c>
+      <c r="E4303" t="n">
+        <v>44610</v>
+      </c>
+      <c r="F4303" t="n">
+        <v>24846</v>
+      </c>
+      <c r="G4303" t="n">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B4304" t="n">
+        <v>161493</v>
+      </c>
+      <c r="C4304" t="n">
+        <v>89702</v>
+      </c>
+      <c r="D4304" t="n">
+        <v>75404</v>
+      </c>
+      <c r="E4304" t="n">
+        <v>49751</v>
+      </c>
+      <c r="F4304" t="n">
+        <v>14298</v>
+      </c>
+      <c r="G4304" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B4305" t="n">
+        <v>161493</v>
+      </c>
+      <c r="C4305" t="n">
+        <v>92129</v>
+      </c>
+      <c r="D4305" t="n">
+        <v>73281</v>
+      </c>
+      <c r="E4305" t="n">
+        <v>55847</v>
+      </c>
+      <c r="F4305" t="n">
+        <v>18848</v>
+      </c>
+      <c r="G4305" t="n">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B4306" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4306" t="n">
+        <v>93337</v>
+      </c>
+      <c r="D4306" t="n">
+        <v>70089</v>
+      </c>
+      <c r="E4306" t="n">
+        <v>48297</v>
+      </c>
+      <c r="F4306" t="n">
+        <v>23248</v>
+      </c>
+      <c r="G4306" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B4307" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4307" t="n">
+        <v>91802</v>
+      </c>
+      <c r="D4307" t="n">
+        <v>71404</v>
+      </c>
+      <c r="E4307" t="n">
+        <v>51838</v>
+      </c>
+      <c r="F4307" t="n">
+        <v>20398</v>
+      </c>
+      <c r="G4307" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B4308" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4308" t="n">
+        <v>92677</v>
+      </c>
+      <c r="D4308" t="n">
+        <v>70755</v>
+      </c>
+      <c r="E4308" t="n">
+        <v>54389</v>
+      </c>
+      <c r="F4308" t="n">
+        <v>21922</v>
+      </c>
+      <c r="G4308" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B4309" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4309" t="n">
+        <v>89662</v>
+      </c>
+      <c r="D4309" t="n">
+        <v>62679</v>
+      </c>
+      <c r="E4309" t="n">
+        <v>44981</v>
+      </c>
+      <c r="F4309" t="n">
+        <v>26983</v>
+      </c>
+      <c r="G4309" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B4310" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4310" t="n">
+        <v>89278</v>
+      </c>
+      <c r="D4310" t="n">
+        <v>63643</v>
+      </c>
+      <c r="E4310" t="n">
+        <v>49240</v>
+      </c>
+      <c r="F4310" t="n">
+        <v>25635</v>
+      </c>
+      <c r="G4310" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B4311" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4311" t="n">
+        <v>90394</v>
+      </c>
+      <c r="D4311" t="n">
+        <v>71321</v>
+      </c>
+      <c r="E4311" t="n">
+        <v>49501</v>
+      </c>
+      <c r="F4311" t="n">
+        <v>19073</v>
+      </c>
+      <c r="G4311" t="n">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B4312" t="n">
+        <v>161615</v>
+      </c>
+      <c r="C4312" t="n">
+        <v>88387</v>
+      </c>
+      <c r="D4312" t="n">
+        <v>72050</v>
+      </c>
+      <c r="E4312" t="n">
+        <v>54509</v>
+      </c>
+      <c r="F4312" t="n">
+        <v>16337</v>
+      </c>
+      <c r="G4312" t="n">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B4313" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4313" t="n">
+        <v>91632</v>
+      </c>
+      <c r="D4313" t="n">
+        <v>70471</v>
+      </c>
+      <c r="E4313" t="n">
+        <v>54677</v>
+      </c>
+      <c r="F4313" t="n">
+        <v>21161</v>
+      </c>
+      <c r="G4313" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B4314" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4314" t="n">
+        <v>92141</v>
+      </c>
+      <c r="D4314" t="n">
+        <v>70617</v>
+      </c>
+      <c r="E4314" t="n">
+        <v>48041</v>
+      </c>
+      <c r="F4314" t="n">
+        <v>21524</v>
+      </c>
+      <c r="G4314" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B4315" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4315" t="n">
+        <v>90637</v>
+      </c>
+      <c r="D4315" t="n">
+        <v>69256</v>
+      </c>
+      <c r="E4315" t="n">
+        <v>53365</v>
+      </c>
+      <c r="F4315" t="n">
+        <v>21381</v>
+      </c>
+      <c r="G4315" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B4316" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4316" t="n">
+        <v>87612</v>
+      </c>
+      <c r="D4316" t="n">
+        <v>62181</v>
+      </c>
+      <c r="E4316" t="n">
+        <v>53540</v>
+      </c>
+      <c r="F4316" t="n">
+        <v>25431</v>
+      </c>
+      <c r="G4316" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B4317" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4317" t="n">
+        <v>88513</v>
+      </c>
+      <c r="D4317" t="n">
+        <v>61549</v>
+      </c>
+      <c r="E4317" t="n">
+        <v>49871</v>
+      </c>
+      <c r="F4317" t="n">
+        <v>26964</v>
+      </c>
+      <c r="G4317" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B4318" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4318" t="n">
+        <v>88685</v>
+      </c>
+      <c r="D4318" t="n">
+        <v>70932</v>
+      </c>
+      <c r="E4318" t="n">
+        <v>48702</v>
+      </c>
+      <c r="F4318" t="n">
+        <v>17753</v>
+      </c>
+      <c r="G4318" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B4319" t="n">
+        <v>161918</v>
+      </c>
+      <c r="C4319" t="n">
+        <v>94309</v>
+      </c>
+      <c r="D4319" t="n">
+        <v>70637</v>
+      </c>
+      <c r="E4319" t="n">
+        <v>45713</v>
+      </c>
+      <c r="F4319" t="n">
+        <v>23672</v>
+      </c>
+      <c r="G4319" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
